--- a/src_files/data_files/industrialCHP.xlsx
+++ b/src_files/data_files/industrialCHP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E523FC-77B3-413F-8437-B871745C60B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8208D61D-DB7F-421B-A6D4-E4E897A2ED1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="799" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="17520" tabRatio="799" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="unitdata" sheetId="8" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="131">
   <si>
     <t>Country</t>
   </si>
@@ -175,12 +175,6 @@
     <t>all</t>
   </si>
   <si>
-    <t>Industry non-renewable CHP</t>
-  </si>
-  <si>
-    <t>Industry renewable CHP</t>
-  </si>
-  <si>
     <t>demand (TWh)</t>
   </si>
   <si>
@@ -458,6 +452,15 @@
   </si>
   <si>
     <t>nodeBalance</t>
+  </si>
+  <si>
+    <t>Hard-coded names</t>
+  </si>
+  <si>
+    <t>coalCHPIndustry</t>
+  </si>
+  <si>
+    <t>bioCHPIndustry</t>
   </si>
 </sst>
 </file>
@@ -588,7 +591,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,6 +692,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -796,7 +805,7 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -945,6 +954,8 @@
     <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -953,9 +964,6 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="26">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1129,18 +1137,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="0" tint="-0.14999847407452621"/>
@@ -1247,6 +1243,9 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1297,30 +1296,30 @@
     <tableColumn id="3" xr3:uid="{57483FE3-C6A9-426F-9DF7-4926168CE122}" name="Node_suffix"/>
     <tableColumn id="4" xr3:uid="{F155858A-1910-4203-8242-FCFC753CE0F1}" name="Scenario" dataDxfId="23"/>
     <tableColumn id="5" xr3:uid="{2976D6D8-21B5-4358-9605-474352CC3FAF}" name="Year" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{5D7C3B58-23CE-4BD9-9814-7BCAEB987C3B}" name="nodeBalance" dataDxfId="0" dataCellStyle="Normal 3"/>
-    <tableColumn id="6" xr3:uid="{894F3647-7759-4FB2-B8B6-24582E443654}" name="upwardLimit" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{622B05A3-F0D0-4BEE-B5E5-8AA1239444AE}" name="reference" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{FB556C05-FAE9-43E0-9FC0-D26AB24EC6BC}" name="balancePenalty" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{7EAD7D20-CDA2-446F-BC00-8EC30C32C13B}" name="selfDischargeLoss" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{078F1241-6AF8-480F-897B-1DA7DB1520F6}" name="maxSpill" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{5D7C3B58-23CE-4BD9-9814-7BCAEB987C3B}" name="nodeBalance" dataDxfId="21" dataCellStyle="Normal 3"/>
+    <tableColumn id="6" xr3:uid="{894F3647-7759-4FB2-B8B6-24582E443654}" name="upwardLimit" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{622B05A3-F0D0-4BEE-B5E5-8AA1239444AE}" name="reference" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{FB556C05-FAE9-43E0-9FC0-D26AB24EC6BC}" name="balancePenalty" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{7EAD7D20-CDA2-446F-BC00-8EC30C32C13B}" name="selfDischargeLoss" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{078F1241-6AF8-480F-897B-1DA7DB1520F6}" name="maxSpill" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{20DC892E-7082-4467-928B-8F4B2C671031}" name="Table1" displayName="Table1" ref="A1:I28" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{20DC892E-7082-4467-928B-8F4B2C671031}" name="Table1" displayName="Table1" ref="A1:I28" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" tableBorderDxfId="13">
   <autoFilter ref="A1:I28" xr:uid="{20DC892E-7082-4467-928B-8F4B2C671031}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{90B3BA90-E856-467E-A12E-718C92D72014}" name="Country" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{47E364C8-C977-4369-A805-4B42B4F3422D}" name="Generator_ID" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{D50F5294-47D2-4C56-800B-3E44FF430FA7}" name="Scenario" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{649C99FE-77E1-437E-9EDE-D888843F1482}" name="Year" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{1A49AF74-6C24-40D6-B37A-D2ADAB4DE02B}" name="capacity_input1" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{F30D702A-E7C4-4705-81A5-A391EA397049}" name="capacity_output1" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{B74AC38E-95FA-433D-B521-50231B26F101}" name="node_suffix_output2" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{2E1D1700-DA32-4625-8DFD-E756415F2202}" name="capacity_output2" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{89275BD6-4B5C-4E77-BA1F-FF40DDEF4E2A}" name="Note" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{90B3BA90-E856-467E-A12E-718C92D72014}" name="Country" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{32B812CD-1C93-4CE6-9A43-B9AE59998316}" name="unittype" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{D50F5294-47D2-4C56-800B-3E44FF430FA7}" name="Scenario" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{649C99FE-77E1-437E-9EDE-D888843F1482}" name="Year" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{1A49AF74-6C24-40D6-B37A-D2ADAB4DE02B}" name="capacity_input1" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{F30D702A-E7C4-4705-81A5-A391EA397049}" name="capacity_output1" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{B74AC38E-95FA-433D-B521-50231B26F101}" name="node_suffix_output2" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{2E1D1700-DA32-4625-8DFD-E756415F2202}" name="capacity_output2" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{89275BD6-4B5C-4E77-BA1F-FF40DDEF4E2A}" name="Note" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1596,14 +1595,15 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="12" customWidth="1"/>
-    <col min="4" max="4" width="12" style="12" customWidth="1"/>
-    <col min="5" max="6" width="24.7109375" style="12" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="21.7109375" style="12" customWidth="1"/>
-    <col min="9" max="9" width="27.140625" style="12" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="12" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" style="12" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" style="12" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" style="12" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="57" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="C1" s="57" t="s">
         <v>2</v>
@@ -1635,15 +1635,15 @@
         <v>8</v>
       </c>
       <c r="J1" s="57" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>34</v>
@@ -1653,15 +1653,15 @@
       </c>
       <c r="E2" s="12">
         <f>F2/0.4</f>
-        <v>2113</v>
+        <v>1901.5</v>
       </c>
       <c r="F2" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A2), 1)</f>
-        <v>845.2</v>
+        <v>760.6</v>
       </c>
       <c r="G2" s="12">
         <f>ROUND(F2/(0.5+0.16666), 1)</f>
-        <v>1267.8</v>
+        <v>1140.9000000000001</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>28</v>
@@ -1676,7 +1676,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>34</v>
@@ -1706,10 +1706,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>34</v>
@@ -1719,15 +1719,15 @@
       </c>
       <c r="E4" s="12">
         <f t="shared" ref="E4" si="3">F4/0.4</f>
-        <v>1416.5</v>
+        <v>1064.7499999999998</v>
       </c>
       <c r="F4" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A4), 1)</f>
-        <v>566.6</v>
+        <v>425.9</v>
       </c>
       <c r="G4" s="12">
         <f t="shared" ref="G4" si="4">ROUND(F4/(0.5+0.16666), 1)</f>
-        <v>849.9</v>
+        <v>638.9</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>28</v>
@@ -1742,7 +1742,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>34</v>
@@ -1752,15 +1752,15 @@
       </c>
       <c r="E5" s="12">
         <f t="shared" si="0"/>
-        <v>18200</v>
+        <v>32669</v>
       </c>
       <c r="F5" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A5), 1)</f>
-        <v>7280</v>
+        <v>13067.6</v>
       </c>
       <c r="G5" s="12">
         <f t="shared" si="1"/>
-        <v>10920.1</v>
+        <v>19601.599999999999</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>28</v>
@@ -1772,10 +1772,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>34</v>
@@ -1808,7 +1808,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>34</v>
@@ -1841,7 +1841,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>34</v>
@@ -1851,15 +1851,15 @@
       </c>
       <c r="E8" s="12">
         <f t="shared" si="0"/>
-        <v>622.25</v>
+        <v>663.25</v>
       </c>
       <c r="F8" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A8), 1)</f>
-        <v>248.9</v>
+        <v>265.3</v>
       </c>
       <c r="G8" s="12">
         <f t="shared" si="1"/>
-        <v>373.4</v>
+        <v>398</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>28</v>
@@ -1874,7 +1874,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>34</v>
@@ -1884,15 +1884,15 @@
       </c>
       <c r="E9" s="12">
         <f t="shared" si="0"/>
-        <v>9950</v>
+        <v>4325</v>
       </c>
       <c r="F9" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A9), 1)</f>
-        <v>3980</v>
+        <v>1730</v>
       </c>
       <c r="G9" s="12">
         <f t="shared" si="1"/>
-        <v>5970.1</v>
+        <v>2595</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>28</v>
@@ -1907,7 +1907,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>34</v>
@@ -1917,15 +1917,15 @@
       </c>
       <c r="E10" s="12">
         <f t="shared" si="0"/>
-        <v>976.25</v>
+        <v>6562</v>
       </c>
       <c r="F10" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A10), 1)</f>
-        <v>390.5</v>
+        <v>2624.8</v>
       </c>
       <c r="G10" s="12">
         <f t="shared" si="1"/>
-        <v>585.79999999999995</v>
+        <v>3937.2</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>28</v>
@@ -1940,7 +1940,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>34</v>
@@ -1950,15 +1950,15 @@
       </c>
       <c r="E11" s="12">
         <f t="shared" si="0"/>
-        <v>11000</v>
+        <v>6065</v>
       </c>
       <c r="F11" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A11), 1)</f>
-        <v>4400</v>
+        <v>2426</v>
       </c>
       <c r="G11" s="12">
         <f t="shared" si="1"/>
-        <v>6600.1</v>
+        <v>3639</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>28</v>
@@ -1973,7 +1973,7 @@
         <v>23</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>34</v>
@@ -1983,15 +1983,15 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" si="0"/>
-        <v>493.25</v>
+        <v>622</v>
       </c>
       <c r="F12" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A12), 1)</f>
-        <v>197.3</v>
+        <v>248.8</v>
       </c>
       <c r="G12" s="12">
         <f t="shared" si="1"/>
-        <v>296</v>
+        <v>373.2</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>28</v>
@@ -2006,7 +2006,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>34</v>
@@ -2016,22 +2016,22 @@
       </c>
       <c r="E13" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>198.75</v>
       </c>
       <c r="F13" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A13), 1)</f>
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="G13" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>119.3</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>28</v>
       </c>
       <c r="J13" s="68" t="str">
         <f t="shared" si="2"/>
-        <v>remove</v>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -2039,7 +2039,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>34</v>
@@ -2072,7 +2072,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>34</v>
@@ -2082,22 +2082,22 @@
       </c>
       <c r="E15" s="12">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F15" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A15), 1)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G15" s="12">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>28</v>
       </c>
       <c r="J15" s="68" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>remove</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2105,7 +2105,7 @@
         <v>27</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>34</v>
@@ -2115,22 +2115,22 @@
       </c>
       <c r="E16" s="12">
         <f t="shared" si="0"/>
-        <v>487.5</v>
+        <v>0</v>
       </c>
       <c r="F16" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A16), 1)</f>
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="G16" s="12">
         <f t="shared" si="1"/>
-        <v>292.5</v>
+        <v>0</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>28</v>
       </c>
       <c r="J16" s="68" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>remove</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2138,7 +2138,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>34</v>
@@ -2148,22 +2148,22 @@
       </c>
       <c r="E17" s="12">
         <f t="shared" si="0"/>
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F17" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A17), 1)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>28</v>
       </c>
       <c r="J17" s="68" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>remove</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2171,7 +2171,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>34</v>
@@ -2181,15 +2181,15 @@
       </c>
       <c r="E18" s="12">
         <f t="shared" si="0"/>
-        <v>14035.75</v>
+        <v>5387.7499999999991</v>
       </c>
       <c r="F18" s="68">
         <f>ROUND(SUMIFS(Summary!$W:$W,Summary!$I:$I, $A18), 1)</f>
-        <v>5614.3</v>
+        <v>2155.1</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="1"/>
-        <v>8421.5</v>
+        <v>3232.7</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>28</v>
@@ -2204,7 +2204,7 @@
         <v>26</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>34</v>
@@ -2237,7 +2237,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>34</v>
@@ -2270,7 +2270,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>34</v>
@@ -2303,7 +2303,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>34</v>
@@ -2336,7 +2336,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>34</v>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>34</v>
@@ -2379,15 +2379,15 @@
       </c>
       <c r="E24" s="12">
         <f t="shared" si="0"/>
-        <v>1901.5</v>
+        <v>2113</v>
       </c>
       <c r="F24" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A24), 1)</f>
-        <v>760.6</v>
+        <v>845.2</v>
       </c>
       <c r="G24" s="12">
         <f t="shared" si="1"/>
-        <v>1140.9000000000001</v>
+        <v>1267.8</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>28</v>
@@ -2402,7 +2402,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>34</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>34</v>
@@ -2445,15 +2445,15 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" ref="E26" si="5">F26/0.4</f>
-        <v>1064.7499999999998</v>
+        <v>1416.5</v>
       </c>
       <c r="F26" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A26), 1)</f>
-        <v>425.9</v>
+        <v>566.6</v>
       </c>
       <c r="G26" s="12">
         <f t="shared" ref="G26" si="6">ROUND(F26/(0.5+0.16666), 1)</f>
-        <v>638.9</v>
+        <v>849.9</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>9</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>34</v>
@@ -2478,15 +2478,15 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="0"/>
-        <v>32669</v>
+        <v>18200</v>
       </c>
       <c r="F27" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A27), 1)</f>
-        <v>13067.6</v>
+        <v>7280</v>
       </c>
       <c r="G27" s="12">
         <f t="shared" si="1"/>
-        <v>19601.599999999999</v>
+        <v>10920.1</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>28</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>34</v>
@@ -2534,7 +2534,7 @@
         <v>19</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>34</v>
@@ -2567,7 +2567,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>34</v>
@@ -2577,15 +2577,15 @@
       </c>
       <c r="E30" s="12">
         <f t="shared" si="0"/>
-        <v>774</v>
+        <v>733.25</v>
       </c>
       <c r="F30" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A30), 1)</f>
-        <v>309.60000000000002</v>
+        <v>293.3</v>
       </c>
       <c r="G30" s="12">
         <f t="shared" si="1"/>
-        <v>464.4</v>
+        <v>440</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>28</v>
@@ -2600,7 +2600,7 @@
         <v>12</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>34</v>
@@ -2610,15 +2610,15 @@
       </c>
       <c r="E31" s="12">
         <f t="shared" si="0"/>
-        <v>4325</v>
+        <v>9950</v>
       </c>
       <c r="F31" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A31), 1)</f>
-        <v>1730</v>
+        <v>3980</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="1"/>
-        <v>2595</v>
+        <v>5970.1</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>28</v>
@@ -2633,7 +2633,7 @@
         <v>20</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>34</v>
@@ -2643,15 +2643,15 @@
       </c>
       <c r="E32" s="12">
         <f t="shared" si="0"/>
-        <v>6562</v>
+        <v>976.25</v>
       </c>
       <c r="F32" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A32), 1)</f>
-        <v>2624.8</v>
+        <v>390.5</v>
       </c>
       <c r="G32" s="12">
         <f t="shared" si="1"/>
-        <v>3937.2</v>
+        <v>585.79999999999995</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>28</v>
@@ -2666,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>34</v>
@@ -2676,15 +2676,15 @@
       </c>
       <c r="E33" s="12">
         <f t="shared" si="0"/>
-        <v>6065</v>
+        <v>11000</v>
       </c>
       <c r="F33" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A33), 1)</f>
-        <v>2426</v>
+        <v>4400</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="1"/>
-        <v>3639</v>
+        <v>6600.1</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>28</v>
@@ -2699,7 +2699,7 @@
         <v>23</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>34</v>
@@ -2709,15 +2709,15 @@
       </c>
       <c r="E34" s="12">
         <f t="shared" si="0"/>
-        <v>967.99999999999989</v>
+        <v>839.24999999999989</v>
       </c>
       <c r="F34" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A34), 1)</f>
-        <v>387.2</v>
+        <v>335.7</v>
       </c>
       <c r="G34" s="12">
         <f t="shared" si="1"/>
-        <v>580.79999999999995</v>
+        <v>503.6</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>28</v>
@@ -2732,7 +2732,7 @@
         <v>24</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>34</v>
@@ -2742,15 +2742,15 @@
       </c>
       <c r="E35" s="12">
         <f t="shared" si="0"/>
-        <v>732.99999999999989</v>
+        <v>534.24999999999989</v>
       </c>
       <c r="F35" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A35), 1)</f>
-        <v>293.2</v>
+        <v>213.7</v>
       </c>
       <c r="G35" s="12">
         <f t="shared" si="1"/>
-        <v>439.8</v>
+        <v>320.60000000000002</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>28</v>
@@ -2765,7 +2765,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>34</v>
@@ -2798,7 +2798,7 @@
         <v>21</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>34</v>
@@ -2808,22 +2808,22 @@
       </c>
       <c r="E37" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F37" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A37), 1)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>28</v>
       </c>
       <c r="J37" s="68" t="str">
         <f t="shared" si="2"/>
-        <v>remove</v>
+        <v/>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2831,7 +2831,7 @@
         <v>27</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>34</v>
@@ -2841,22 +2841,22 @@
       </c>
       <c r="E38" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>487.5</v>
       </c>
       <c r="F38" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A38), 1)</f>
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="G38" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>292.5</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>28</v>
       </c>
       <c r="J38" s="68" t="str">
         <f t="shared" si="2"/>
-        <v>remove</v>
+        <v/>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2864,7 +2864,7 @@
         <v>22</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>34</v>
@@ -2874,22 +2874,22 @@
       </c>
       <c r="E39" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F39" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A39), 1)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G39" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H39" s="12" t="s">
         <v>28</v>
       </c>
       <c r="J39" s="68" t="str">
         <f t="shared" si="2"/>
-        <v>remove</v>
+        <v/>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2897,7 +2897,7 @@
         <v>13</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>34</v>
@@ -2907,15 +2907,15 @@
       </c>
       <c r="E40" s="12">
         <f t="shared" si="0"/>
-        <v>5387.7499999999991</v>
+        <v>14035.75</v>
       </c>
       <c r="F40" s="69">
         <f>ROUND(SUMIFS(Summary!$V:$V,Summary!$I:$I, $A40), 1)</f>
-        <v>2155.1</v>
+        <v>5614.3</v>
       </c>
       <c r="G40" s="12">
         <f t="shared" si="1"/>
-        <v>3232.7</v>
+        <v>8421.5</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>28</v>
@@ -2930,7 +2930,7 @@
         <v>26</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>34</v>
@@ -2963,7 +2963,7 @@
         <v>16</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>34</v>
@@ -2996,7 +2996,7 @@
         <v>17</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>34</v>
@@ -3029,7 +3029,7 @@
         <v>18</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>34</v>
@@ -3062,7 +3062,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>34</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>33</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>33</v>
@@ -3601,12 +3601,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:A17 G5:G17 B5:F23">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:G4">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3651,27 +3651,27 @@
         <v>3</v>
       </c>
       <c r="F1" s="67" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G1" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="J1" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="K1" s="61" t="s">
         <v>123</v>
-      </c>
-      <c r="J1" s="61" t="s">
-        <v>124</v>
-      </c>
-      <c r="K1" s="61" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="62" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B2" s="58" t="s">
         <v>33</v>
@@ -3723,7 +3723,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="62" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B4" s="58" t="s">
         <v>33</v>
@@ -3775,7 +3775,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="62" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B6" s="58" t="s">
         <v>33</v>
@@ -4266,7 +4266,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="B3:Z31"/>
+  <dimension ref="B2:Z31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="16.28515625" style="47" customWidth="1"/>
@@ -4275,168 +4275,194 @@
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
     <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="17" width="8.85546875" customWidth="1"/>
+    <col min="16" max="17" width="24.28515625" customWidth="1"/>
     <col min="18" max="24" width="14" customWidth="1"/>
     <col min="26" max="26" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="P2" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q2" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="S2" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="T2" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="V2" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="W2" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y2" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z2" s="73" t="s">
+        <v>128</v>
+      </c>
+    </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C3" s="38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E3" s="38"/>
       <c r="F3" s="38" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K3" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="L3" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="N3" s="38" t="s">
         <v>109</v>
-      </c>
-      <c r="L3" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" s="38" t="s">
-        <v>111</v>
       </c>
       <c r="O3" s="38"/>
       <c r="R3" s="38" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="S3" s="38"/>
       <c r="T3" s="38"/>
       <c r="U3" s="38" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C4" s="38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D4" s="38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E4" s="38"/>
       <c r="F4" s="38" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J4" s="47" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K4" s="47" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L4" s="47" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="O4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" t="s">
         <v>36</v>
       </c>
-      <c r="Q4" t="s">
-        <v>35</v>
+      <c r="P4" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q4" s="72" t="s">
+        <v>130</v>
       </c>
       <c r="R4" t="s">
-        <v>38</v>
-      </c>
-      <c r="S4" t="s">
         <v>36</v>
       </c>
-      <c r="T4" t="s">
-        <v>35</v>
+      <c r="S4" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="T4" s="72" t="s">
+        <v>130</v>
       </c>
       <c r="U4" t="s">
-        <v>38</v>
-      </c>
-      <c r="V4" t="s">
         <v>36</v>
       </c>
-      <c r="W4" t="s">
-        <v>35</v>
+      <c r="V4" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="W4" s="72" t="s">
+        <v>130</v>
       </c>
       <c r="X4" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y4" t="s">
         <v>36</v>
       </c>
-      <c r="Z4" t="s">
-        <v>35</v>
+      <c r="Y4" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z4" s="72" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C5" s="47" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E5" s="47"/>
       <c r="F5" s="47" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J5" s="47" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K5" s="47" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L5" s="47" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N5" s="47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P5" s="47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q5" s="47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="R5" s="47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="S5" s="47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="T5" s="47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="U5" s="45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="V5" s="45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="W5" s="45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="X5" s="45" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Y5" s="45" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Z5" s="45" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C6" s="56" t="e">
         <f t="shared" ref="C6:C15" si="0">J6*10^6/$O6 / 8760</f>
@@ -4452,7 +4478,7 @@
         <v>0.8956448761979382</v>
       </c>
       <c r="I6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J6" s="49">
         <f>SUMIFS('H2Heavy, demands'!$F$2:$F$15,'H2Heavy, demands'!$A$2:$A$15,Summary!$I6)</f>
@@ -4489,11 +4515,11 @@
       </c>
       <c r="S6" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I6,  TYNDP2024!$B:$B,S$4)</f>
-        <v>760.64499999999998</v>
+        <v>845.24</v>
       </c>
       <c r="T6" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I6,  TYNDP2024!$B:$B,T$4)</f>
-        <v>845.24</v>
+        <v>760.64499999999998</v>
       </c>
       <c r="U6" s="53">
         <f>R6</f>
@@ -4501,11 +4527,11 @@
       </c>
       <c r="V6" s="53">
         <f t="shared" ref="V6" si="3">S6</f>
-        <v>760.64499999999998</v>
+        <v>845.24</v>
       </c>
       <c r="W6" s="53">
         <f t="shared" ref="W6" si="4">T6</f>
-        <v>845.24</v>
+        <v>760.64499999999998</v>
       </c>
       <c r="X6" s="46">
         <f t="shared" ref="X6:X15" si="5">IF(ISNUMBER(U6), U6/(0.5+0.16666), "-")</f>
@@ -4513,11 +4539,11 @@
       </c>
       <c r="Y6" s="46">
         <f t="shared" ref="Y6" si="6">IF(ISNUMBER(V6), V6/(0.5+0.16666), "-")</f>
-        <v>1140.9789097890978</v>
+        <v>1267.8726787267872</v>
       </c>
       <c r="Z6" s="46">
         <f t="shared" ref="Z6" si="7">IF(ISNUMBER(W6), W6/(0.5+0.16666), "-")</f>
-        <v>1267.8726787267872</v>
+        <v>1140.9789097890978</v>
       </c>
     </row>
     <row r="7" spans="2:26" x14ac:dyDescent="0.25">
@@ -4575,11 +4601,11 @@
       </c>
       <c r="S7" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I7,  TYNDP2024!$B:$B,S$4)</f>
-        <v>614.625</v>
+        <v>1594</v>
       </c>
       <c r="T7" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I7,  TYNDP2024!$B:$B,T$4)</f>
-        <v>1594</v>
+        <v>614.625</v>
       </c>
       <c r="U7" s="54">
         <f t="shared" ref="U7" si="8">N7</f>
@@ -4608,7 +4634,7 @@
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C8" s="56" t="e">
         <f t="shared" si="0"/>
@@ -4662,11 +4688,11 @@
       </c>
       <c r="S8" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I8,  TYNDP2024!$B:$B,S$4)</f>
-        <v>425.88900000000001</v>
+        <v>566.59900000000005</v>
       </c>
       <c r="T8" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I8,  TYNDP2024!$B:$B,T$4)</f>
-        <v>566.59900000000005</v>
+        <v>425.88900000000001</v>
       </c>
       <c r="U8" s="53">
         <f>R8</f>
@@ -4674,11 +4700,11 @@
       </c>
       <c r="V8" s="53">
         <f t="shared" ref="V8" si="11">S8</f>
-        <v>425.88900000000001</v>
+        <v>566.59900000000005</v>
       </c>
       <c r="W8" s="53">
         <f t="shared" ref="W8" si="12">T8</f>
-        <v>566.59900000000005</v>
+        <v>425.88900000000001</v>
       </c>
       <c r="X8" s="46">
         <f t="shared" si="5"/>
@@ -4686,11 +4712,11 @@
       </c>
       <c r="Y8" s="46">
         <f>IF(ISNUMBER(V8), V8/(0.5+0.16666), "-")</f>
-        <v>638.839888398884</v>
+        <v>849.90699906999077</v>
       </c>
       <c r="Z8" s="46">
         <f>IF(ISNUMBER(W8), W8/(0.5+0.16666), "-")</f>
-        <v>849.90699906999077</v>
+        <v>638.839888398884</v>
       </c>
     </row>
     <row r="9" spans="2:26" x14ac:dyDescent="0.25">
@@ -4748,11 +4774,11 @@
       </c>
       <c r="S9" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I9,  TYNDP2024!$B:$B,S$4)</f>
-        <v>13067.585999999999</v>
+        <v>7280.02</v>
       </c>
       <c r="T9" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I9,  TYNDP2024!$B:$B,T$4)</f>
-        <v>7280.02</v>
+        <v>13067.585999999999</v>
       </c>
       <c r="U9" s="53">
         <f>R9</f>
@@ -4760,11 +4786,11 @@
       </c>
       <c r="V9" s="53">
         <f t="shared" ref="V9:V16" si="13">S9</f>
-        <v>13067.585999999999</v>
+        <v>7280.02</v>
       </c>
       <c r="W9" s="53">
         <f t="shared" ref="W9:W16" si="14">T9</f>
-        <v>7280.02</v>
+        <v>13067.585999999999</v>
       </c>
       <c r="X9" s="46">
         <f t="shared" si="5"/>
@@ -4772,16 +4798,16 @@
       </c>
       <c r="Y9" s="46">
         <f t="shared" ref="Y9:Y29" si="15">IF(ISNUMBER(V9), V9/(0.5+0.16666), "-")</f>
-        <v>19601.575015750157</v>
+        <v>10920.139201392014</v>
       </c>
       <c r="Z9" s="46">
         <f t="shared" ref="Z9:Z29" si="16">IF(ISNUMBER(W9), W9/(0.5+0.16666), "-")</f>
-        <v>10920.139201392014</v>
+        <v>19601.575015750157</v>
       </c>
     </row>
     <row r="10" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B10" s="70" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C10" s="56" t="e">
         <f t="shared" si="0"/>
@@ -4797,7 +4823,7 @@
         <v>-</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J10" s="49"/>
       <c r="K10" s="49">
@@ -4852,7 +4878,7 @@
     </row>
     <row r="11" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B11" s="44" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C11" s="56" t="e">
         <f t="shared" si="0"/>
@@ -4868,7 +4894,7 @@
         <v>-</v>
       </c>
       <c r="I11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J11" s="49"/>
       <c r="K11" s="49">
@@ -4876,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="49" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M11" s="40"/>
       <c r="N11" s="46">
@@ -4908,13 +4934,13 @@
         <v>0</v>
       </c>
       <c r="U11" s="46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="V11" s="46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="W11" s="46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="X11" s="46" t="str">
         <f t="shared" si="5"/>
@@ -4958,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="49" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M12" s="40"/>
       <c r="N12" s="46">
@@ -4983,20 +5009,20 @@
       </c>
       <c r="S12" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I12,  TYNDP2024!$B:$B,S$4)</f>
-        <v>7.26</v>
+        <v>0</v>
       </c>
       <c r="T12" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I12,  TYNDP2024!$B:$B,T$4)</f>
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="U12" s="46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="V12" s="46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="W12" s="46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="X12" s="46" t="str">
         <f t="shared" si="5"/>
@@ -5066,11 +5092,11 @@
       </c>
       <c r="S13" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I13,  TYNDP2024!$B:$B,S$4)</f>
-        <v>167.65</v>
+        <v>134.952</v>
       </c>
       <c r="T13" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I13,  TYNDP2024!$B:$B,T$4)</f>
-        <v>134.952</v>
+        <v>167.65</v>
       </c>
       <c r="U13" s="55">
         <f>AVERAGE(N13,R13)</f>
@@ -5078,11 +5104,11 @@
       </c>
       <c r="V13" s="55">
         <f t="shared" ref="V13:W13" si="18">AVERAGE(P13,S13)</f>
-        <v>309.63799513304201</v>
+        <v>293.28899513304202</v>
       </c>
       <c r="W13" s="55">
         <f t="shared" si="18"/>
-        <v>248.93287108905164</v>
+        <v>265.28187108905166</v>
       </c>
       <c r="X13" s="46">
         <f t="shared" si="5"/>
@@ -5090,11 +5116,11 @@
       </c>
       <c r="Y13" s="46">
         <f t="shared" si="17"/>
-        <v>464.46163731593617</v>
+        <v>439.9378920784838</v>
       </c>
       <c r="Z13" s="46">
         <f t="shared" si="17"/>
-        <v>373.40304066398409</v>
+        <v>397.92678590143652</v>
       </c>
     </row>
     <row r="14" spans="2:26" x14ac:dyDescent="0.25">
@@ -5152,11 +5178,11 @@
       </c>
       <c r="S14" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I14,  TYNDP2024!$B:$B,S$4)</f>
-        <v>1730</v>
+        <v>3980.011</v>
       </c>
       <c r="T14" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I14,  TYNDP2024!$B:$B,T$4)</f>
-        <v>3980.011</v>
+        <v>1730</v>
       </c>
       <c r="U14" s="53">
         <f>R14</f>
@@ -5164,11 +5190,11 @@
       </c>
       <c r="V14" s="53">
         <f>S14</f>
-        <v>1730</v>
+        <v>3980.011</v>
       </c>
       <c r="W14" s="53">
         <f>T14</f>
-        <v>3980.011</v>
+        <v>1730</v>
       </c>
       <c r="X14" s="46">
         <f t="shared" si="5"/>
@@ -5176,11 +5202,11 @@
       </c>
       <c r="Y14" s="46">
         <f t="shared" si="17"/>
-        <v>2595.0259502595027</v>
+        <v>5970.0762007620069</v>
       </c>
       <c r="Z14" s="46">
         <f t="shared" si="17"/>
-        <v>5970.0762007620069</v>
+        <v>2595.0259502595027</v>
       </c>
     </row>
     <row r="15" spans="2:26" x14ac:dyDescent="0.25">
@@ -5238,11 +5264,11 @@
       </c>
       <c r="S15" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I15,  TYNDP2024!$B:$B,S$4)</f>
-        <v>2624.82</v>
+        <v>390.5</v>
       </c>
       <c r="T15" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I15,  TYNDP2024!$B:$B,T$4)</f>
-        <v>390.5</v>
+        <v>2624.82</v>
       </c>
       <c r="U15" s="53">
         <f>R15</f>
@@ -5250,11 +5276,11 @@
       </c>
       <c r="V15" s="53">
         <f t="shared" ref="V15" si="19">S15</f>
-        <v>2624.82</v>
+        <v>390.5</v>
       </c>
       <c r="W15" s="53">
         <f t="shared" ref="W15" si="20">T15</f>
-        <v>390.5</v>
+        <v>2624.82</v>
       </c>
       <c r="X15" s="46">
         <f t="shared" si="5"/>
@@ -5262,11 +5288,11 @@
       </c>
       <c r="Y15" s="46">
         <f t="shared" si="17"/>
-        <v>3937.2693726937268</v>
+        <v>585.7558575585756</v>
       </c>
       <c r="Z15" s="46">
         <f t="shared" si="17"/>
-        <v>585.7558575585756</v>
+        <v>3937.2693726937268</v>
       </c>
     </row>
     <row r="16" spans="2:26" x14ac:dyDescent="0.25">
@@ -5324,11 +5350,11 @@
       </c>
       <c r="S16" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I16,  TYNDP2024!$B:$B,S$4)</f>
-        <v>2426</v>
+        <v>4400</v>
       </c>
       <c r="T16" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I16,  TYNDP2024!$B:$B,T$4)</f>
-        <v>4400</v>
+        <v>2426</v>
       </c>
       <c r="U16" s="53">
         <f>R16</f>
@@ -5336,11 +5362,11 @@
       </c>
       <c r="V16" s="53">
         <f t="shared" si="13"/>
-        <v>2426</v>
+        <v>4400</v>
       </c>
       <c r="W16" s="53">
         <f t="shared" si="14"/>
-        <v>4400</v>
+        <v>2426</v>
       </c>
       <c r="X16" s="46">
         <f t="shared" ref="X16:X29" si="24">IF(ISNUMBER(U16), U16/(0.5+0.16666), "-")</f>
@@ -5348,11 +5374,11 @@
       </c>
       <c r="Y16" s="46">
         <f t="shared" si="15"/>
-        <v>3639.0363903639036</v>
+        <v>6600.0660006600065</v>
       </c>
       <c r="Z16" s="46">
         <f t="shared" si="16"/>
-        <v>6600.0660006600065</v>
+        <v>3639.0363903639036</v>
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.25">
@@ -5410,11 +5436,11 @@
       </c>
       <c r="S17" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I17,  TYNDP2024!$B:$B,S$4)</f>
-        <v>209.89</v>
+        <v>106.89</v>
       </c>
       <c r="T17" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I17,  TYNDP2024!$B:$B,T$4)</f>
-        <v>106.89</v>
+        <v>209.89</v>
       </c>
       <c r="U17" s="55">
         <f>AVERAGE(N17,R17)</f>
@@ -5422,11 +5448,11 @@
       </c>
       <c r="V17" s="55">
         <f>AVERAGE(P17,S17)</f>
-        <v>387.21124391630252</v>
+        <v>335.71124391630252</v>
       </c>
       <c r="W17" s="55">
         <f>AVERAGE(Q17,T17)</f>
-        <v>197.26637190021125</v>
+        <v>248.76637190021125</v>
       </c>
       <c r="X17" s="46">
         <f t="shared" ref="X17:Z23" si="27">IF(ISNUMBER(U17), U17/(0.5+0.16666), "-")</f>
@@ -5434,11 +5460,11 @@
       </c>
       <c r="Y17" s="46">
         <f t="shared" si="27"/>
-        <v>580.82267410119482</v>
+        <v>503.5719015934697</v>
       </c>
       <c r="Z17" s="46">
         <f t="shared" si="27"/>
-        <v>295.90251687548562</v>
+        <v>373.15328938321068</v>
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.25">
@@ -5496,11 +5522,11 @@
       </c>
       <c r="S18" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I18,  TYNDP2024!$B:$B,S$4)</f>
-        <v>159.018</v>
+        <v>0</v>
       </c>
       <c r="T18" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I18,  TYNDP2024!$B:$B,T$4)</f>
-        <v>0</v>
+        <v>159.018</v>
       </c>
       <c r="U18" s="55">
         <f>AVERAGE(N18,R18)</f>
@@ -5508,11 +5534,11 @@
       </c>
       <c r="V18" s="55">
         <f>AVERAGE(P18,S18)</f>
-        <v>293.22487039377194</v>
+        <v>213.71587039377192</v>
       </c>
       <c r="W18" s="55">
         <f>AVERAGE(Q18,T18)</f>
-        <v>0</v>
+        <v>79.509</v>
       </c>
       <c r="X18" s="46">
         <f t="shared" si="27"/>
@@ -5520,11 +5546,11 @@
       </c>
       <c r="Y18" s="46">
         <f t="shared" si="27"/>
-        <v>439.84170400769796</v>
+        <v>320.57701136077145</v>
       </c>
       <c r="Z18" s="46">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>119.26469264692646</v>
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.25">
@@ -5582,11 +5608,11 @@
       </c>
       <c r="S19" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I19,  TYNDP2024!$B:$B,S$4)</f>
-        <v>415</v>
+        <v>4381.5</v>
       </c>
       <c r="T19" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I19,  TYNDP2024!$B:$B,T$4)</f>
-        <v>4381.5</v>
+        <v>415</v>
       </c>
       <c r="U19" s="54">
         <f t="shared" ref="U19" si="28">N19</f>
@@ -5615,7 +5641,7 @@
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B20" s="70" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C20" s="56" t="e">
         <f t="shared" si="25"/>
@@ -5631,7 +5657,7 @@
         <v>-</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J20" s="49"/>
       <c r="K20" s="49">
@@ -5739,11 +5765,11 @@
       </c>
       <c r="S21" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I21,  TYNDP2024!$B:$B,S$4)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T21" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I21,  TYNDP2024!$B:$B,T$4)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U21" s="53">
         <f t="shared" ref="U21:W23" si="31">R21</f>
@@ -5751,11 +5777,11 @@
       </c>
       <c r="V21" s="53">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W21" s="53">
         <f t="shared" si="31"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="X21" s="46">
         <f t="shared" si="27"/>
@@ -5763,11 +5789,11 @@
       </c>
       <c r="Y21" s="46">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>30.000300003000028</v>
       </c>
       <c r="Z21" s="46">
         <f t="shared" si="27"/>
-        <v>30.000300003000028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.25">
@@ -5825,11 +5851,11 @@
       </c>
       <c r="S22" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I22,  TYNDP2024!$B:$B,S$4)</f>
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="T22" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I22,  TYNDP2024!$B:$B,T$4)</f>
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="U22" s="53">
         <f t="shared" si="31"/>
@@ -5837,11 +5863,11 @@
       </c>
       <c r="V22" s="53">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="W22" s="53">
         <f t="shared" si="31"/>
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="X22" s="46">
         <f t="shared" si="27"/>
@@ -5849,11 +5875,11 @@
       </c>
       <c r="Y22" s="46">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>292.50292502925026</v>
       </c>
       <c r="Z22" s="46">
         <f t="shared" si="27"/>
-        <v>292.50292502925026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:26" x14ac:dyDescent="0.25">
@@ -5911,11 +5937,11 @@
       </c>
       <c r="S23" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I23,  TYNDP2024!$B:$B,S$4)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T23" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I23,  TYNDP2024!$B:$B,T$4)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U23" s="53">
         <f t="shared" si="31"/>
@@ -5923,11 +5949,11 @@
       </c>
       <c r="V23" s="53">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W23" s="53">
         <f t="shared" si="31"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X23" s="46">
         <f t="shared" si="27"/>
@@ -5935,11 +5961,11 @@
       </c>
       <c r="Y23" s="46">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>75.000750007500073</v>
       </c>
       <c r="Z23" s="46">
         <f t="shared" si="27"/>
-        <v>75.000750007500073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.25">
@@ -5997,11 +6023,11 @@
       </c>
       <c r="S24" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I24,  TYNDP2024!$B:$B,S$4)</f>
-        <v>2155.0540000000001</v>
+        <v>5614.3209999999999</v>
       </c>
       <c r="T24" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I24,  TYNDP2024!$B:$B,T$4)</f>
-        <v>5614.3209999999999</v>
+        <v>2155.0540000000001</v>
       </c>
       <c r="U24" s="53">
         <f>R24</f>
@@ -6009,11 +6035,11 @@
       </c>
       <c r="V24" s="53">
         <f t="shared" ref="V24" si="32">S24</f>
-        <v>2155.0540000000001</v>
+        <v>5614.3209999999999</v>
       </c>
       <c r="W24" s="53">
         <f t="shared" ref="W24" si="33">T24</f>
-        <v>5614.3209999999999</v>
+        <v>2155.0540000000001</v>
       </c>
       <c r="X24" s="46">
         <f t="shared" si="24"/>
@@ -6021,16 +6047,16 @@
       </c>
       <c r="Y24" s="46">
         <f t="shared" si="15"/>
-        <v>3232.6133261332611</v>
+        <v>8421.565715657156</v>
       </c>
       <c r="Z24" s="46">
         <f t="shared" si="16"/>
-        <v>8421.565715657156</v>
+        <v>3232.6133261332611</v>
       </c>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B25" s="70" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C25" s="56" t="e">
         <f t="shared" si="21"/>
@@ -6046,7 +6072,7 @@
         <v>-</v>
       </c>
       <c r="I25" s="44" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J25" s="49"/>
       <c r="K25" s="49">
@@ -6154,11 +6180,11 @@
       </c>
       <c r="S26" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I26,  TYNDP2024!$B:$B,S$4)</f>
-        <v>198.7</v>
+        <v>0</v>
       </c>
       <c r="T26" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I26,  TYNDP2024!$B:$B,T$4)</f>
-        <v>0</v>
+        <v>198.7</v>
       </c>
       <c r="U26" s="54">
         <f t="shared" ref="U26:U29" si="35">N26</f>
@@ -6240,11 +6266,11 @@
       </c>
       <c r="S27" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I27,  TYNDP2024!$B:$B,S$4)</f>
-        <v>743.57</v>
+        <v>0</v>
       </c>
       <c r="T27" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I27,  TYNDP2024!$B:$B,T$4)</f>
-        <v>0</v>
+        <v>743.57</v>
       </c>
       <c r="U27" s="54">
         <f t="shared" si="35"/>
@@ -6326,11 +6352,11 @@
       </c>
       <c r="S28" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I28,  TYNDP2024!$B:$B,S$4)</f>
-        <v>2818.0549999999998</v>
+        <v>0</v>
       </c>
       <c r="T28" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I28,  TYNDP2024!$B:$B,T$4)</f>
-        <v>0</v>
+        <v>2818.0549999999998</v>
       </c>
       <c r="U28" s="54">
         <f t="shared" si="35"/>
@@ -6412,11 +6438,11 @@
       </c>
       <c r="S29" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I29,  TYNDP2024!$B:$B,S$4)</f>
-        <v>698.09</v>
+        <v>0</v>
       </c>
       <c r="T29" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I29,  TYNDP2024!$B:$B,T$4)</f>
-        <v>0</v>
+        <v>698.09</v>
       </c>
       <c r="U29" s="54">
         <f t="shared" si="35"/>
@@ -6498,11 +6524,11 @@
       </c>
       <c r="S30" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I30,  TYNDP2024!$B:$B,S$4)</f>
-        <v>2906.1660000000002</v>
+        <v>8657.1929999999993</v>
       </c>
       <c r="T30" s="46">
         <f>SUMIFS(TYNDP2024!$C:$C,TYNDP2024!$A:$A,Summary!$I30,  TYNDP2024!$B:$B,T$4)</f>
-        <v>8657.1929999999993</v>
+        <v>2906.1660000000002</v>
       </c>
       <c r="U30" s="54">
         <f t="shared" ref="U30" si="39">N30</f>
@@ -6544,7 +6570,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" style="12" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" style="12" customWidth="1"/>
     <col min="4" max="4" width="12" style="12" customWidth="1"/>
     <col min="5" max="5" width="17" style="12" customWidth="1"/>
@@ -6558,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>2</v>
@@ -6587,7 +6613,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>34</v>
@@ -6614,7 +6640,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>34</v>
@@ -6641,7 +6667,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>34</v>
@@ -6668,7 +6694,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>34</v>
@@ -6695,7 +6721,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>34</v>
@@ -6722,7 +6748,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>34</v>
@@ -6749,7 +6775,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>34</v>
@@ -6776,7 +6802,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>34</v>
@@ -6803,7 +6829,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>34</v>
@@ -6830,7 +6856,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>34</v>
@@ -6857,7 +6883,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>34</v>
@@ -6884,7 +6910,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>34</v>
@@ -6911,7 +6937,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>34</v>
@@ -6938,7 +6964,7 @@
         <v>24</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>34</v>
@@ -6965,7 +6991,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>34</v>
@@ -6992,7 +7018,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>34</v>
@@ -7019,7 +7045,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>34</v>
@@ -7046,7 +7072,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>34</v>
@@ -7073,7 +7099,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>34</v>
@@ -7100,7 +7126,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>34</v>
@@ -7127,7 +7153,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>34</v>
@@ -7154,7 +7180,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>34</v>
@@ -7181,7 +7207,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>34</v>
@@ -7208,7 +7234,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>34</v>
@@ -7235,7 +7261,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>34</v>
@@ -7262,7 +7288,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>34</v>
@@ -7289,7 +7315,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>34</v>
@@ -7317,7 +7343,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:I28">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7648,7 +7674,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:G15">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7664,6 +7690,8 @@
     <col min="1" max="1" width="10.140625" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9.140625" style="47"/>
+    <col min="11" max="11" width="39.85546875" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -7671,7 +7699,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C1" s="45">
         <v>2030</v>
@@ -7684,26 +7712,26 @@
       <c r="A2" s="38"/>
       <c r="B2" s="38"/>
       <c r="C2" s="45" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D2" s="45" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C3" s="46">
         <f>SUMIFS($N:$N,$J:$J,$A3,$K:$K,$B3,$M:$M,C$1)</f>
-        <v>760.64499999999998</v>
+        <v>845.24</v>
       </c>
       <c r="D3" s="46">
         <f t="shared" ref="D3:D46" si="0">SUMIFS($N:$N,$J:$J,$A3,$K:$K,$B3,$M:$M,D$1)</f>
-        <v>760.64499999999998</v>
+        <v>845.24</v>
       </c>
       <c r="J3" s="65" t="s">
         <v>0</v>
@@ -7726,24 +7754,24 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C4" s="46">
         <f t="shared" ref="C4:C24" si="1">SUMIFS($N:$N,$J:$J,$A4,$K:$K,$B4,$M:$M,C$1)</f>
-        <v>614.625</v>
+        <v>1594</v>
       </c>
       <c r="D4" s="46">
         <f t="shared" si="0"/>
-        <v>614.625</v>
+        <v>1594</v>
       </c>
       <c r="J4" s="66" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K4" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L4" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M4" s="66">
         <v>2030</v>
@@ -7754,27 +7782,27 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C5" s="46">
         <f t="shared" si="1"/>
-        <v>425.88900000000001</v>
+        <v>566.59900000000005</v>
       </c>
       <c r="D5" s="46">
         <f t="shared" si="0"/>
-        <v>621.351</v>
+        <v>440.44200000000001</v>
       </c>
       <c r="J5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K5" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M5">
         <v>2030</v>
@@ -7788,24 +7816,24 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C6" s="46">
         <f t="shared" si="1"/>
-        <v>13067.585999999999</v>
+        <v>7280.02</v>
       </c>
       <c r="D6" s="46">
         <f t="shared" si="0"/>
-        <v>5835.1959999999999</v>
+        <v>2340.1</v>
       </c>
       <c r="J6" s="66" t="s">
         <v>15</v>
       </c>
       <c r="K6" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L6" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M6" s="66">
         <v>2030</v>
@@ -7816,10 +7844,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C7" s="46">
         <f t="shared" si="1"/>
@@ -7833,10 +7861,10 @@
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M7">
         <v>2030</v>
@@ -7850,24 +7878,24 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C8" s="46">
         <f t="shared" si="1"/>
-        <v>7.26</v>
+        <v>0</v>
       </c>
       <c r="D8" s="46">
         <f t="shared" si="0"/>
-        <v>7.26</v>
+        <v>0</v>
       </c>
       <c r="J8" s="66" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K8" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L8" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M8" s="66">
         <v>2030</v>
@@ -7881,24 +7909,24 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C9" s="46">
         <f t="shared" si="1"/>
-        <v>167.65</v>
+        <v>134.952</v>
       </c>
       <c r="D9" s="46">
         <f t="shared" si="0"/>
-        <v>134.65</v>
+        <v>134.952</v>
       </c>
       <c r="J9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K9" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M9">
         <v>2030</v>
@@ -7912,24 +7940,24 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C10" s="46">
         <f t="shared" si="1"/>
-        <v>1730</v>
+        <v>3980.011</v>
       </c>
       <c r="D10" s="46">
         <f t="shared" si="0"/>
-        <v>1730</v>
+        <v>3980.011</v>
       </c>
       <c r="J10" s="66" t="s">
         <v>9</v>
       </c>
       <c r="K10" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L10" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M10" s="66">
         <v>2030</v>
@@ -7943,24 +7971,24 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C11" s="46">
         <f t="shared" si="1"/>
-        <v>2624.82</v>
+        <v>390.5</v>
       </c>
       <c r="D11" s="46">
         <f t="shared" si="0"/>
-        <v>2624.82</v>
+        <v>133</v>
       </c>
       <c r="J11" t="s">
         <v>9</v>
       </c>
       <c r="K11" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M11">
         <v>2030</v>
@@ -7974,24 +8002,24 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C12" s="46">
         <f t="shared" si="1"/>
-        <v>2426</v>
+        <v>4400</v>
       </c>
       <c r="D12" s="46">
         <f t="shared" si="0"/>
-        <v>2451.06</v>
+        <v>600.04</v>
       </c>
       <c r="J12" s="66" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L12" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M12" s="66">
         <v>2030</v>
@@ -8005,24 +8033,24 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C13" s="46">
         <f t="shared" si="1"/>
-        <v>209.89</v>
+        <v>106.89</v>
       </c>
       <c r="D13" s="46">
         <f t="shared" si="0"/>
-        <v>209.89</v>
+        <v>106.89</v>
       </c>
       <c r="J13" t="s">
         <v>25</v>
       </c>
       <c r="K13" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M13">
         <v>2030</v>
@@ -8036,24 +8064,24 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C14" s="46">
         <f t="shared" si="1"/>
-        <v>159.018</v>
+        <v>0</v>
       </c>
       <c r="D14" s="46">
         <f t="shared" si="0"/>
-        <v>299.92700000000002</v>
+        <v>0</v>
       </c>
       <c r="J14" s="66" t="s">
         <v>25</v>
       </c>
       <c r="K14" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L14" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M14" s="66">
         <v>2030</v>
@@ -8067,24 +8095,24 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C15" s="46">
         <f t="shared" si="1"/>
-        <v>415</v>
+        <v>4381.5</v>
       </c>
       <c r="D15" s="46">
         <f t="shared" si="0"/>
-        <v>208.6</v>
+        <v>1722.5</v>
       </c>
       <c r="J15" t="s">
         <v>12</v>
       </c>
       <c r="K15" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15">
         <v>2030</v>
@@ -8098,24 +8126,24 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C16" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D16" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J16" s="66" t="s">
         <v>12</v>
       </c>
       <c r="K16" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L16" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M16" s="66">
         <v>2030</v>
@@ -8129,24 +8157,24 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C17" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="D17" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="J17" t="s">
         <v>20</v>
       </c>
       <c r="K17" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M17">
         <v>2030</v>
@@ -8160,24 +8188,24 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C18" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D18" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J18" s="66" t="s">
         <v>20</v>
       </c>
       <c r="K18" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L18" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M18" s="66">
         <v>2030</v>
@@ -8191,24 +8219,24 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C19" s="46">
         <f t="shared" si="1"/>
-        <v>2155.0540000000001</v>
+        <v>5614.3209999999999</v>
       </c>
       <c r="D19" s="46">
         <f t="shared" si="0"/>
-        <v>1969.3689999999999</v>
+        <v>4402.0529999999999</v>
       </c>
       <c r="J19" t="s">
         <v>10</v>
       </c>
       <c r="K19" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M19">
         <v>2030</v>
@@ -8222,24 +8250,24 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C20" s="46">
         <f t="shared" si="1"/>
-        <v>198.7</v>
+        <v>0</v>
       </c>
       <c r="D20" s="46">
         <f t="shared" si="0"/>
-        <v>198.7</v>
+        <v>0</v>
       </c>
       <c r="J20" s="66" t="s">
         <v>10</v>
       </c>
       <c r="K20" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L20" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M20" s="66">
         <v>2030</v>
@@ -8253,24 +8281,24 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C21" s="46">
         <f t="shared" si="1"/>
-        <v>743.57</v>
+        <v>0</v>
       </c>
       <c r="D21" s="46">
         <f t="shared" si="0"/>
-        <v>743.57</v>
+        <v>0</v>
       </c>
       <c r="J21" t="s">
         <v>23</v>
       </c>
       <c r="K21" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M21">
         <v>2030</v>
@@ -8284,24 +8312,24 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C22" s="46">
         <f t="shared" si="1"/>
-        <v>2818.0549999999998</v>
+        <v>0</v>
       </c>
       <c r="D22" s="46">
         <f t="shared" si="0"/>
-        <v>2554.0549999999998</v>
+        <v>0</v>
       </c>
       <c r="J22" s="66" t="s">
         <v>23</v>
       </c>
       <c r="K22" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L22" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M22" s="66">
         <v>2030</v>
@@ -8315,24 +8343,24 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C23" s="46">
         <f t="shared" si="1"/>
-        <v>698.09</v>
+        <v>0</v>
       </c>
       <c r="D23" s="46">
         <f t="shared" si="0"/>
-        <v>698.09</v>
+        <v>0</v>
       </c>
       <c r="J23" t="s">
         <v>24</v>
       </c>
       <c r="K23" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L23" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M23">
         <v>2030</v>
@@ -8346,24 +8374,24 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C24" s="46">
         <f t="shared" si="1"/>
-        <v>2906.1660000000002</v>
+        <v>8657.1929999999993</v>
       </c>
       <c r="D24" s="46">
         <f t="shared" si="0"/>
-        <v>8155.7269999999999</v>
+        <v>26148.173999999999</v>
       </c>
       <c r="J24" s="66" t="s">
         <v>14</v>
       </c>
       <c r="K24" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L24" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M24" s="66">
         <v>2030</v>
@@ -8374,27 +8402,27 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C25" s="46">
         <f t="shared" ref="C25:C46" si="2">SUMIFS($N:$N,$J:$J,$A25,$K:$K,$B25,$M:$M,C$1)</f>
-        <v>845.24</v>
+        <v>760.64499999999998</v>
       </c>
       <c r="D25" s="46">
         <f t="shared" si="0"/>
-        <v>845.24</v>
+        <v>760.64499999999998</v>
       </c>
       <c r="J25" t="s">
         <v>14</v>
       </c>
       <c r="K25" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M25">
         <v>2030</v>
@@ -8408,24 +8436,24 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C26" s="46">
         <f t="shared" si="2"/>
-        <v>1594</v>
+        <v>614.625</v>
       </c>
       <c r="D26" s="46">
         <f t="shared" si="0"/>
-        <v>1594</v>
+        <v>614.625</v>
       </c>
       <c r="J26" s="66" t="s">
         <v>21</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M26" s="66">
         <v>2030</v>
@@ -8436,27 +8464,27 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C27" s="46">
         <f t="shared" si="2"/>
-        <v>566.59900000000005</v>
+        <v>425.88900000000001</v>
       </c>
       <c r="D27" s="46">
         <f t="shared" si="0"/>
-        <v>440.44200000000001</v>
+        <v>621.351</v>
       </c>
       <c r="J27" t="s">
         <v>27</v>
       </c>
       <c r="K27" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L27" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M27">
         <v>2030</v>
@@ -8470,24 +8498,24 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C28" s="46">
         <f t="shared" si="2"/>
-        <v>7280.02</v>
+        <v>13067.585999999999</v>
       </c>
       <c r="D28" s="46">
         <f t="shared" si="0"/>
-        <v>2340.1</v>
+        <v>5835.1959999999999</v>
       </c>
       <c r="J28" s="66" t="s">
         <v>22</v>
       </c>
       <c r="K28" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M28" s="66">
         <v>2030</v>
@@ -8498,10 +8526,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C29" s="46">
         <f t="shared" si="2"/>
@@ -8515,10 +8543,10 @@
         <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M29">
         <v>2030</v>
@@ -8532,24 +8560,24 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C30" s="46">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="D30" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="J30" s="66" t="s">
         <v>13</v>
       </c>
       <c r="K30" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L30" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M30" s="66">
         <v>2030</v>
@@ -8563,24 +8591,24 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C31" s="46">
         <f t="shared" si="2"/>
-        <v>134.952</v>
+        <v>167.65</v>
       </c>
       <c r="D31" s="46">
         <f t="shared" si="0"/>
-        <v>134.952</v>
+        <v>134.65</v>
       </c>
       <c r="J31" t="s">
         <v>26</v>
       </c>
       <c r="K31" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M31">
         <v>2030</v>
@@ -8594,24 +8622,24 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C32" s="46">
         <f t="shared" si="2"/>
-        <v>3980.011</v>
+        <v>1730</v>
       </c>
       <c r="D32" s="46">
         <f t="shared" si="0"/>
-        <v>3980.011</v>
+        <v>1730</v>
       </c>
       <c r="J32" s="66" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M32" s="66">
         <v>2030</v>
@@ -8625,24 +8653,24 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C33" s="46">
         <f t="shared" si="2"/>
-        <v>390.5</v>
+        <v>2624.82</v>
       </c>
       <c r="D33" s="46">
         <f t="shared" si="0"/>
-        <v>133</v>
+        <v>2624.82</v>
       </c>
       <c r="J33" t="s">
         <v>17</v>
       </c>
       <c r="K33" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M33">
         <v>2030</v>
@@ -8656,24 +8684,24 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C34" s="46">
         <f t="shared" si="2"/>
-        <v>4400</v>
+        <v>2426</v>
       </c>
       <c r="D34" s="46">
         <f t="shared" si="0"/>
-        <v>600.04</v>
+        <v>2451.06</v>
       </c>
       <c r="J34" s="66" t="s">
         <v>18</v>
       </c>
       <c r="K34" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M34" s="66">
         <v>2030</v>
@@ -8687,24 +8715,24 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C35" s="46">
         <f t="shared" si="2"/>
-        <v>106.89</v>
+        <v>209.89</v>
       </c>
       <c r="D35" s="46">
         <f t="shared" si="0"/>
-        <v>106.89</v>
+        <v>209.89</v>
       </c>
       <c r="J35" t="s">
         <v>11</v>
       </c>
       <c r="K35" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M35">
         <v>2030</v>
@@ -8718,24 +8746,24 @@
         <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C36" s="46">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>159.018</v>
       </c>
       <c r="D36" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>299.92700000000002</v>
       </c>
       <c r="J36" s="66" t="s">
         <v>11</v>
       </c>
       <c r="K36" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L36" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M36" s="66">
         <v>2030</v>
@@ -8749,24 +8777,24 @@
         <v>14</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C37" s="46">
         <f t="shared" si="2"/>
-        <v>4381.5</v>
+        <v>415</v>
       </c>
       <c r="D37" s="46">
         <f t="shared" si="0"/>
-        <v>1722.5</v>
+        <v>208.6</v>
       </c>
       <c r="J37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K37" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L37" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M37">
         <v>2040</v>
@@ -8780,24 +8808,24 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C38" s="46">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D38" s="46">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J38" s="66" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K38" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L38" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M38" s="66">
         <v>2040</v>
@@ -8811,24 +8839,24 @@
         <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C39" s="46">
         <f t="shared" si="2"/>
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="D39" s="46">
         <f t="shared" si="0"/>
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="J39" t="s">
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L39" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M39">
         <v>2040</v>
@@ -8842,24 +8870,24 @@
         <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C40" s="46">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D40" s="46">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J40" s="66" t="s">
         <v>15</v>
       </c>
       <c r="K40" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L40" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M40" s="66">
         <v>2040</v>
@@ -8873,24 +8901,24 @@
         <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C41" s="46">
         <f t="shared" si="2"/>
-        <v>5614.3209999999999</v>
+        <v>2155.0540000000001</v>
       </c>
       <c r="D41" s="46">
         <f t="shared" si="0"/>
-        <v>4402.0529999999999</v>
+        <v>1969.3689999999999</v>
       </c>
       <c r="J41" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K41" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L41" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M41">
         <v>2040</v>
@@ -8904,24 +8932,24 @@
         <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C42" s="46">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>198.7</v>
       </c>
       <c r="D42" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>198.7</v>
       </c>
       <c r="J42" s="66" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K42" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L42" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M42" s="66">
         <v>2040</v>
@@ -8935,24 +8963,24 @@
         <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C43" s="46">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>743.57</v>
       </c>
       <c r="D43" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>743.57</v>
       </c>
       <c r="J43" t="s">
         <v>9</v>
       </c>
       <c r="K43" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L43" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M43">
         <v>2040</v>
@@ -8966,24 +8994,24 @@
         <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C44" s="46">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2818.0549999999998</v>
       </c>
       <c r="D44" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2554.0549999999998</v>
       </c>
       <c r="J44" s="66" t="s">
         <v>9</v>
       </c>
       <c r="K44" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L44" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M44" s="66">
         <v>2040</v>
@@ -8997,24 +9025,24 @@
         <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C45" s="46">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>698.09</v>
       </c>
       <c r="D45" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>698.09</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
       </c>
       <c r="K45" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L45" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M45">
         <v>2040</v>
@@ -9028,24 +9056,24 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C46" s="46">
         <f t="shared" si="2"/>
-        <v>8657.1929999999993</v>
+        <v>2906.1660000000002</v>
       </c>
       <c r="D46" s="46">
         <f t="shared" si="0"/>
-        <v>26148.173999999999</v>
+        <v>8155.7269999999999</v>
       </c>
       <c r="J46" s="66" t="s">
         <v>25</v>
       </c>
       <c r="K46" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L46" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M46" s="66">
         <v>2040</v>
@@ -9059,10 +9087,10 @@
         <v>25</v>
       </c>
       <c r="K47" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M47">
         <v>2040</v>
@@ -9076,10 +9104,10 @@
         <v>12</v>
       </c>
       <c r="K48" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L48" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M48" s="66">
         <v>2040</v>
@@ -9093,10 +9121,10 @@
         <v>12</v>
       </c>
       <c r="K49" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M49">
         <v>2040</v>
@@ -9110,10 +9138,10 @@
         <v>20</v>
       </c>
       <c r="K50" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L50" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M50" s="66">
         <v>2040</v>
@@ -9127,10 +9155,10 @@
         <v>20</v>
       </c>
       <c r="K51" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L51" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M51">
         <v>2040</v>
@@ -9144,10 +9172,10 @@
         <v>10</v>
       </c>
       <c r="K52" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L52" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M52" s="66">
         <v>2040</v>
@@ -9161,10 +9189,10 @@
         <v>10</v>
       </c>
       <c r="K53" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M53">
         <v>2040</v>
@@ -9178,10 +9206,10 @@
         <v>23</v>
       </c>
       <c r="K54" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L54" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M54" s="66">
         <v>2040</v>
@@ -9195,10 +9223,10 @@
         <v>23</v>
       </c>
       <c r="K55" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L55" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M55">
         <v>2040</v>
@@ -9212,10 +9240,10 @@
         <v>24</v>
       </c>
       <c r="K56" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L56" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M56" s="66">
         <v>2040</v>
@@ -9229,10 +9257,10 @@
         <v>14</v>
       </c>
       <c r="K57" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L57" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M57">
         <v>2040</v>
@@ -9246,10 +9274,10 @@
         <v>14</v>
       </c>
       <c r="K58" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L58" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M58" s="66">
         <v>2040</v>
@@ -9263,10 +9291,10 @@
         <v>21</v>
       </c>
       <c r="K59" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L59" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M59">
         <v>2040</v>
@@ -9280,10 +9308,10 @@
         <v>27</v>
       </c>
       <c r="K60" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L60" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M60" s="66">
         <v>2040</v>
@@ -9297,10 +9325,10 @@
         <v>22</v>
       </c>
       <c r="K61" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L61" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M61">
         <v>2040</v>
@@ -9314,10 +9342,10 @@
         <v>13</v>
       </c>
       <c r="K62" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L62" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M62" s="66">
         <v>2040</v>
@@ -9331,10 +9359,10 @@
         <v>13</v>
       </c>
       <c r="K63" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L63" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M63">
         <v>2040</v>
@@ -9348,10 +9376,10 @@
         <v>26</v>
       </c>
       <c r="K64" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L64" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M64" s="66">
         <v>2040</v>
@@ -9365,10 +9393,10 @@
         <v>16</v>
       </c>
       <c r="K65" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L65" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M65">
         <v>2040</v>
@@ -9382,10 +9410,10 @@
         <v>17</v>
       </c>
       <c r="K66" s="66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L66" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M66" s="66">
         <v>2040</v>
@@ -9399,10 +9427,10 @@
         <v>18</v>
       </c>
       <c r="K67" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L67" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M67">
         <v>2040</v>
@@ -9416,10 +9444,10 @@
         <v>11</v>
       </c>
       <c r="K68" s="66" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L68" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M68" s="66">
         <v>2040</v>
@@ -9433,10 +9461,10 @@
         <v>11</v>
       </c>
       <c r="K69" s="64" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L69" s="64" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M69" s="64">
         <v>2040</v>
@@ -9464,17 +9492,17 @@
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
@@ -9489,10 +9517,10 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
@@ -9506,10 +9534,10 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
@@ -9536,11 +9564,11 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9" s="24"/>
       <c r="C9" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24"/>
@@ -9553,11 +9581,11 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B10" s="24"/>
       <c r="C10" s="26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="24"/>
@@ -9570,11 +9598,11 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B11" s="24"/>
       <c r="C11" s="26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="24"/>
@@ -9587,11 +9615,11 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B12" s="24"/>
       <c r="C12" s="26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="24"/>
@@ -9604,11 +9632,11 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B13" s="24"/>
       <c r="C13" s="26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="24"/>
@@ -9621,11 +9649,11 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="24"/>
@@ -9641,7 +9669,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B16" s="37">
         <v>2014</v>
@@ -9674,7 +9702,7 @@
         <v>2023</v>
       </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N16" s="39">
         <v>2023</v>
@@ -9691,42 +9719,42 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G17" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H17" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K17" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B18" s="34">
         <v>199505.277</v>
@@ -9761,7 +9789,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B19" s="33">
         <v>168075.02799999999</v>
@@ -9796,7 +9824,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B20" s="36">
         <v>9510.5</v>
@@ -9850,7 +9878,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B21" s="35">
         <v>244</v>
@@ -9901,7 +9929,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B22" s="36">
         <v>8267</v>
@@ -9934,7 +9962,7 @@
         <v>7211.7110000000002</v>
       </c>
       <c r="M22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N22" s="41" cm="1">
         <f t="array" ref="N22">TREND($B22:$K22,$B$16:$K$16,N$16)</f>
@@ -9955,7 +9983,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B23" s="33">
         <v>2602.2489999999998</v>
@@ -9988,7 +10016,7 @@
         <v>5425.9210000000003</v>
       </c>
       <c r="M23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N23" s="41" cm="1">
         <f t="array" ref="N23">TREND($B23:$K23,$B$16:$K$16,N$16)</f>
@@ -10009,7 +10037,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B24" s="36">
         <v>42176</v>
@@ -10063,7 +10091,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B25" s="35">
         <v>52</v>
@@ -10117,7 +10145,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B26" s="34">
         <v>2037.1969999999999</v>
@@ -10168,7 +10196,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B27" s="35">
         <v>1680</v>
@@ -10219,7 +10247,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B28" s="36">
         <v>30870</v>
@@ -10273,7 +10301,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B29" s="33">
         <v>15474.468999999999</v>
@@ -10327,7 +10355,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B30" s="36">
         <v>326</v>
@@ -10378,7 +10406,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B31" s="33">
         <v>15143.832</v>
@@ -10429,7 +10457,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B32" s="34">
         <v>78.233000000000004</v>
@@ -10480,7 +10508,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B33" s="35">
         <v>244</v>
@@ -10534,7 +10562,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B34" s="36">
         <v>690</v>
@@ -10588,7 +10616,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B35" s="33">
         <v>269.36399999999998</v>
@@ -10639,7 +10667,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B36" s="36">
         <v>592</v>
@@ -10690,7 +10718,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B37" s="35">
         <v>75</v>
@@ -10741,7 +10769,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B38" s="34">
         <v>20698.989000000001</v>
@@ -10795,7 +10823,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B39" s="33">
         <v>7321.277</v>
@@ -10828,7 +10856,7 @@
         <v>12981.643</v>
       </c>
       <c r="M39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N39" s="41" cm="1">
         <f t="array" ref="N39">TREND($B39:$K39,$B$16:$K$16,N$16)</f>
@@ -10849,7 +10877,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B40" s="36">
         <v>8383</v>
@@ -10903,7 +10931,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B41" s="33">
         <v>8435.1669999999995</v>
@@ -10954,7 +10982,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B42" s="36">
         <v>5747</v>
@@ -11005,7 +11033,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B43" s="35">
         <v>720</v>
@@ -11056,7 +11084,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B44" s="36">
         <v>2623</v>
@@ -11107,7 +11135,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B45" s="35">
         <v>9650</v>
@@ -11161,7 +11189,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B46" s="36">
         <v>5595</v>
@@ -11194,7 +11222,7 @@
         <v>7876</v>
       </c>
       <c r="M46" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N46" s="41" cm="1">
         <f t="array" ref="N46">TREND($B46:$K46,$B$16:$K$16,N$16)</f>
@@ -11215,7 +11243,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B47" s="35">
         <v>0</v>
@@ -11242,10 +11270,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K47" s="31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N47" s="41" t="e" cm="1">
         <f t="array" ref="N47">TREND($B47:$K47,$B$16:$K$16,N$16)</f>
@@ -11266,7 +11294,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B48" s="36">
         <v>0</v>
@@ -11317,7 +11345,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="29" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B49" s="35">
         <v>2900</v>
@@ -11350,7 +11378,7 @@
         <v>2347.1770000000001</v>
       </c>
       <c r="M49" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N49" s="41" cm="1">
         <f t="array" ref="N49">TREND($B49:$K49,$B$16:$K$16,N$16)</f>
@@ -11371,7 +11399,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B50" s="36">
         <v>39057</v>
@@ -11392,16 +11420,16 @@
         <v>58189.074999999997</v>
       </c>
       <c r="H50" s="32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I50" s="32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J50" s="32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K50" s="32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N50" s="41" t="e" cm="1">
         <f t="array" ref="N50">TREND($B50:$K50,$B$16:$K$16,N$16)</f>
@@ -11422,7 +11450,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B51" s="35">
         <v>343</v>
@@ -11473,7 +11501,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B52" s="36">
         <v>0</v>
@@ -11524,7 +11552,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B53" s="35">
         <v>66</v>
@@ -11575,7 +11603,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B54" s="36">
         <v>1</v>
@@ -11626,7 +11654,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B55" s="35">
         <v>0</v>
@@ -11677,7 +11705,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B56" s="36">
         <v>0</v>
@@ -11728,7 +11756,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B57" s="35">
         <v>257</v>
@@ -11758,7 +11786,7 @@
         <v>449.25900000000001</v>
       </c>
       <c r="K57" s="31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N57" s="41" t="e" cm="1">
         <f t="array" ref="N57">TREND($B57:$K57,$B$16:$K$16,N$16)</f>
@@ -11779,7 +11807,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B58" s="36">
         <v>17174</v>
@@ -11830,7 +11858,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="29" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B59" s="35">
         <v>2194</v>
@@ -11854,13 +11882,13 @@
         <v>2460.1999999999998</v>
       </c>
       <c r="I59" s="31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J59" s="31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K59" s="31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N59" s="41" t="e" cm="1">
         <f t="array" ref="N59">TREND($B59:$K59,$B$16:$K$16,N$16)</f>
@@ -11881,7 +11909,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B60" s="36">
         <v>0</v>
@@ -11908,7 +11936,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K60" s="36">
         <v>0</v>
